--- a/sample_data/분개장.xlsx
+++ b/sample_data/분개장.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2355,6 +2355,1695 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>15139200</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 외상매출 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>15139200</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 매출 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>7542400</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1885.6</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 대금 회수(1차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>7569600</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 채권 일부 상계(1차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>27200</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 외환차손 인식(1차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>7605200</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1901.3</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 대금 회수(2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>7569600</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 채권 일부 상계(2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TXN009</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>35600</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Highland Textiles Ltd 외환차익 인식(2차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>원재료매입</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>36980000</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co 원재료매입 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>36980000</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co 외상매입금 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>기말평가</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>280000</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>200000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co 외화환산이익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TXN010</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>기말평가</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>외화환산이익</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>280000</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Kowloon Freight Co 외화환산이익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>9723000</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG 외상매출 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>9723000</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG 매출 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG 대금 회수</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>9723000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG 채권 상계(장부가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TXN011</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>777000</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Alpine Precision AG 외환차익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>원재료매입</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>15237000</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies 원재료매입 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>15237000</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies 외상매입금 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>15237000</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1015.8</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies 채무 상계(장부가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>15126000</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1008.4</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies 대금 지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TXN012</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>111000</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Maple Ridge Supplies 외환차익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp 외상매출 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp 매출 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>980</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp 대금 회수</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>외상매출금(외화)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>22890000</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>915.6</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp 채권 상계(장부가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TXN013</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>결제</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>외환차익</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Outback Mining Corp 외환차익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>원재료매입</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>12939600</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1078.3</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics 원재료매입 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>발생</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>12939600</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1078.3</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics 외상매입금 발생</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>기말평가</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>외상매입금(외화)</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>148800</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1065.9</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics 외화환산이익 인식</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TXN014</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>기말평가</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>외화환산이익</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>148800</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Marina Bay Logistics 외화환산이익 인식</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
